--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -58,11 +58,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +459,7 @@
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
@@ -570,7 +573,11 @@
           <t>https://norns.community/3d/</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>2021-05-27</t>
@@ -599,7 +606,11 @@
           <t>send control voltages out of crow</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CL1MPzJBEmM/?igshid=194nmylkjm8o2</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/42190</t>
@@ -670,7 +681,11 @@
           <t>https://norns.community/4CCFader/</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
@@ -699,7 +714,11 @@
           <t>A Norns instrument of non standard tuning &amp; limitations</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6yVP39R6n48</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/eastwind/64578</t>
@@ -749,7 +768,11 @@
           <t xml:space="preserve">  a customizable pattern and groove midi generator for Monome Norns </t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/_qFI1p-oa7s?si=OWFRrfzndVRUxT2m</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/hiswing-script/71720</t>
@@ -799,7 +822,11 @@
           <t>A sequencer based on fish in a pond</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BK2LxQRKShc</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/koiboi2/73410</t>
@@ -849,7 +876,11 @@
           <t xml:space="preserve"> a powerful and flexible MIDI CC randomizer for the Elektron Machinedrum</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tShiKs0ePec?si=wnLqAmJ0YxB_HlnE</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/machine-drum-randomizer-for-monome-norns/71998</t>
@@ -899,7 +930,11 @@
           <t xml:space="preserve"> a tonal performance utility for the Elektron Machinedrum</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c_i3obivn7A&amp;t=11s</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mdscaler/73236</t>
@@ -949,7 +984,11 @@
           <t xml:space="preserve"> a patch randomizer for Elektron Monomachine</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/yFiYw2ncZfU?si=BeWD4kBgd0KMxcWF</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mnmpatch/71750</t>
@@ -999,7 +1038,11 @@
           <t>a five track sequencer with various sequencer engines per track</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/546873594</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/44781</t>
@@ -1045,7 +1088,11 @@
           <t>Use Just Friends or a MIDI device as a 'melodic' granular synth.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/663336524/55a05fcd1f</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tidbit/52104</t>
@@ -1095,7 +1142,11 @@
           <t>sequence rows of beats with samples</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/474676681</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/abacus/37871</t>
@@ -1141,7 +1192,11 @@
           <t>generative acid basslines.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/670308126</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/acid-test/52201</t>
@@ -1181,9 +1236,7 @@
           <t>jah</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v/>
-      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>sample player engine</t>
@@ -1231,7 +1284,11 @@
           <t>chord sequencer and sampler</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/685262457</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/acrostic/53027</t>
@@ -1277,7 +1334,11 @@
           <t>sampler and mangler of loops</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/535262855?share=copy</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/amen/43746</t>
@@ -1323,7 +1384,11 @@
           <t>this is a dedicated amen break script with 2 knobs - amen and break.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8h3KSgyc4Gk</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/amenbreak/60185</t>
@@ -1369,7 +1434,11 @@
           <t>2D Polyphonic step sequencer for grids</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/yobink/021920003-modular-animator</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/animator/28242</t>
@@ -1415,7 +1484,11 @@
           <t>map arc encoders to up to four parameters (eight with a shift key)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/CfJ71Kugc08/?igshid=MDJmNzVkMjY=</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/arcify/22133</t>
@@ -1461,7 +1534,11 @@
           <t>an interactive environment for designing 2d sound arcologies with norns and grid</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/embed/videoseries?list=PLe1BFUbUceS2N5GLgORKQrw1bsz2ZLwJ3&amp;wmode=transparent&amp;rel=0&amp;autohide=1&amp;showinfo=1&amp;enablejsapi=1</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/arcologies</t>
@@ -1511,7 +1588,11 @@
           <t>check stocks and make music</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B140GeKB3ga/</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/the-arp-index/25182</t>
@@ -1557,7 +1638,11 @@
           <t>a small collection</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/312196152</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/ash-a-small-collection/21349</t>
@@ -1603,7 +1688,11 @@
           <t>adventure game as drone sequencer</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Gr2dT4WEeLg</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/asterion/66602</t>
@@ -1670,7 +1759,11 @@
           <t>https://norns.community/automs70/</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2021-02-07</t>
@@ -1716,7 +1809,11 @@
           <t>https://norns.community/avonlea/</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2025-05-30</t>
@@ -1745,7 +1842,11 @@
           <t>time changes</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/327848801</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/awake/21022</t>
@@ -1791,7 +1892,13 @@
           <t>time drifting</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BYjTCWS-B7o
+https://www.youtube.com/watch?v=Gvr3T7gLltM
+https://www.youtube.com/watch?v=ucVF11lo-m8</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/awake/21022/139</t>
@@ -1837,7 +1944,11 @@
           <t>chimes past</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://w.soundcloud.com/player/?visual=false&amp;url=https%3A%2F%2Fapi.soundcloud.com%2Ftracks%2F695639185&amp;show_artwork=true&amp;maxheight=166</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/awake/21022/38</t>
@@ -1883,7 +1994,11 @@
           <t>Beat repeater with some glitch</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CDef8pQIRA8</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/35047</t>
@@ -1929,7 +2044,11 @@
           <t>a haunted drummer companion</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/shorts/o0VdGHCEDIE</t>
+        </is>
+      </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/bakeneko</t>
@@ -1979,7 +2098,11 @@
           <t>loops sounds into six lfo-modulated voices</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5Lg1fgbTQHM&amp;t=134s</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/barcode/35297</t>
@@ -2025,7 +2148,11 @@
           <t>orbital motion sequencing</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/yncywy/barycenter-demo2</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/barycenter/35980</t>
@@ -2071,7 +2198,11 @@
           <t>keyboard based softcut sample mangler</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pmjxBBTGRH0</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/beacon/</t>
@@ -2121,7 +2252,11 @@
           <t>drum loop re-sequencer</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TiaVWaD2Gjw</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/beets/30069</t>
@@ -2167,7 +2302,11 @@
           <t>chaotic synth</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B6tJ036BuwC/</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/benjolis/28061</t>
@@ -2213,7 +2352,11 @@
           <t>a presscafe remake for Norns</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zw37RrUKMG0</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/bistro/45349</t>
@@ -2280,7 +2423,11 @@
           <t>https://norns.community/bitebeet/</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
@@ -2309,7 +2456,11 @@
           <t>lo-fi FM capable mono/poly</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/696368452?fl=pl&amp;fe=vl</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/bitters-norns</t>
@@ -2355,7 +2506,11 @@
           <t>Bline is a parametric acid-style bassline explorer.</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AHFtgOpIuNQ</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/bline</t>
@@ -2405,7 +2560,11 @@
           <t>blippoo box clone</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_rAutfOZhkQ</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/41107</t>
@@ -2451,7 +2610,11 @@
           <t>a quantized delay with time bending effects</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EJvLCwtocM8</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/blndr/35106</t>
@@ -2497,7 +2660,11 @@
           <t>recreation of Eno and Chilvers' 'bloom' app</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jq_LwMWaq6M</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/bloom/65627</t>
@@ -2547,7 +2714,12 @@
           <t>endless waves</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=frNbtfMnP20
+https://www.instagram.com/reel/CxoFp1WtMoe/?utm_source=ig_web_copy_link&amp;igshid=MzRlODBiNWFlZA==</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/blue/64208</t>
@@ -2593,7 +2765,11 @@
           <t>a bouncing ball sequencer</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/368803868</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/boingg/26536</t>
@@ -2643,7 +2819,11 @@
           <t>stereo delay/looper</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BzFLz_2Adon/</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/23336</t>
@@ -2714,7 +2894,11 @@
           <t>https://norns.community/bowering/</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
           <t>2021-07-08</t>
@@ -2743,7 +2927,11 @@
           <t>sequencer / game</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JS-_MYMZEOk</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/breakthrough/39196</t>
@@ -2793,7 +2981,11 @@
           <t>tidal influencer/activator/lightshow</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/showcase/7782830</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/37639</t>
@@ -2856,7 +3048,11 @@
           <t>https://norns.community/caliper/</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>2021-07-02</t>
@@ -2885,7 +3081,11 @@
           <t>a simple multi-tap delay for the young and young at heart</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MnD8stNB5tE</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/carters-delay-norns/68307</t>
@@ -2931,7 +3131,11 @@
           <t>fifteen midi cc sliders with slewing and recall</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/913013027</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/66147</t>
@@ -2977,7 +3181,11 @@
           <t>ccs for arc dials</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bgwQ0zUg9c4</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/cccccccc/22271</t>
@@ -3023,7 +3231,11 @@
           <t>generate eight connected sine wave lfos and output them over midi</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1vv2tinYUNo</t>
+        </is>
+      </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/changes/33799</t>
@@ -3069,7 +3281,11 @@
           <t>a sample playground</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/480411843</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/cheat-codes-2</t>
@@ -3136,7 +3352,11 @@
           <t>https://norns.community/choukanzu/</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
           <t>2023-08-03</t>
@@ -3165,7 +3385,11 @@
           <t>move cursor. place circles. make music</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/ByL_pJpha8A/</t>
+        </is>
+      </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/22951</t>
@@ -3228,7 +3452,11 @@
           <t>https://norns.community/clarck/</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
           <t>2019-03-07</t>
@@ -3257,7 +3485,11 @@
           <t>punch-in tempo-locked repeating</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CEWzDaXB6VX/</t>
+        </is>
+      </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/clcks/35732</t>
@@ -3320,7 +3552,11 @@
           <t>https://norns.community/clipper/</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>2021-08-24</t>
@@ -3366,7 +3602,11 @@
           <t>https://norns.community/clockabout/</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>2025-02-22</t>
@@ -3395,7 +3635,11 @@
           <t>harmonic performance sequencer</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XBnaCXEn_LU</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/50231</t>
@@ -3441,7 +3685,11 @@
           <t>mod to combine multiple Grids to operate as a single device</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ACd1W_lS7fU</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/65187</t>
@@ -3481,15 +3729,17 @@
           <t>justmat</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v/>
-      </c>
+      <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>combo scripts</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/373927248</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/27020</t>
@@ -3535,7 +3785,11 @@
           <t>asynchronous looper built around the concept of a command sequencer</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/675154727</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/compass/25192</t>
@@ -3585,7 +3839,11 @@
           <t>virtual tape lab</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QOxG_7pYeSw</t>
+        </is>
+      </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/concrete/63575</t>
@@ -3635,7 +3893,11 @@
           <t>scan the stars; make music! an interactive sequencer for Norns, Crow, JF, and midi.</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Exploring Norns Ambient Soundscape #3 (Norns Shield) + Microcosm - Constellations - YouTube</t>
+        </is>
+      </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/constellations/52225</t>
@@ -3681,7 +3943,11 @@
           <t>a grid controlled physics instrument. ported from tehn's m4l script</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4rL78brYvKA</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/46227</t>
@@ -3731,7 +3997,11 @@
           <t>stereo varispeed looper / delay / timeline-smoosher</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bv5klu_l9mp/</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21207</t>
@@ -3802,7 +4072,11 @@
           <t>https://norns.community/crow_talk/</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
           <t>2021-02-13</t>
@@ -3848,7 +4122,11 @@
           <t>https://norns.community/cryptkeeper/</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
           <t>2021-01-14</t>
@@ -3877,7 +4155,11 @@
           <t>mod to send MIDI notes between Norns over IP</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CS-JHFkAdkh/</t>
+        </is>
+      </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/65000</t>
@@ -3927,7 +4209,11 @@
           <t>a drum sequencer based on Mutable Instruments Grids</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/t/cyrene-a-drum-sequencer-based-on-mutable-instruments-grids/31648/32</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/31648</t>
@@ -3977,7 +4263,11 @@
           <t>distort, destroy, downsample and disintegrate</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PmSPPYG9dp4</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/dd/56504</t>
@@ -4023,7 +4313,11 @@
           <t>always looping sample player</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f790xR9Q2Q8</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/delar/63767</t>
@@ -4069,7 +4363,11 @@
           <t>warm delay with modulation and stereo separation</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/970754032</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/40638</t>
@@ -4115,7 +4413,11 @@
           <t>a sequencer but with a mind of its own</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=neXswJJcatc&amp;t=99s</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/delinquencer-a-sequencer-but-with-a-mind-of-its-own/</t>
@@ -4161,7 +4463,11 @@
           <t>a simple noise module but with a mind of its own</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AQ0P7R9CfCY</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/demon-core-a-very-simple-noise-module-for-norns-but-with-a-mind-of-its-own/</t>
@@ -4224,7 +4530,11 @@
           <t>https://norns.community/descartes/</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
@@ -4274,7 +4584,11 @@
           <t>https://norns.community/dimension-expander/</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
           <t>2022-09-22</t>
@@ -4303,7 +4617,11 @@
           <t>record stereo loops while engine loops</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/496475138</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/downtown/40044</t>
@@ -4349,7 +4667,11 @@
           <t>chord-based sequencer, arpeggiator, and harmonizer for norns + grid</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w_qbi_DRllU&amp;list=PL8o_RorYCue6FsMgpDQdhVTmcXPQPBxQW&amp;index=37</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
           <t>http://llllllll.co/t/62607</t>
@@ -4399,7 +4721,11 @@
           <t>drifting relationships creating sequences</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tGZtcpLYWJY</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/drift/36138</t>
@@ -4445,7 +4771,11 @@
           <t>cast drones &amp; record whatever returns</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sYnHYDg3rhg</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/dronecaster</t>
@@ -4495,7 +4825,11 @@
           <t>midi-controlled drum kits</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BzBuAq9B961/</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/23467</t>
@@ -4541,7 +4875,11 @@
           <t>a function sequencer</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/668182244</t>
+        </is>
+      </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/dunes/24790</t>
@@ -4587,7 +4925,11 @@
           <t>a simple granulator, now with optional arc support</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4S1JgGaibV8</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/easygrain/21047</t>
@@ -4633,7 +4975,11 @@
           <t>dual delay / comb filter</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NxpqsLtH880</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/eels/</t>
@@ -4683,7 +5029,11 @@
           <t>polyrhythmic sequencer/sampler using ack</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/426802558</t>
+        </is>
+      </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/ekombi/26812</t>
@@ -4729,7 +5079,11 @@
           <t>shepard tone generator</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CEBgW0SBI-S</t>
+        </is>
+      </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/endless-stairs/34799</t>
@@ -4779,7 +5133,11 @@
           <t>an image sonifier</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/dswKyUUhKMI?si=asedF6KPODwQ288h</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/esper/67885</t>
@@ -4825,7 +5183,11 @@
           <t xml:space="preserve"> six-voice sampler and sequencer</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Mj2-zk-1z2U</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/eterna/73584/</t>
@@ -4875,7 +5237,11 @@
           <t>geometric rhythm generator</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=o9bUmd2UaYc</t>
+        </is>
+      </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/eculidigons/36666</t>
@@ -4921,7 +5287,11 @@
           <t>faeng is a sequencer. inspired by kria. powered by timber.</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/741705623</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/faeng-is-a-sequencer/57871</t>
@@ -4967,7 +5337,11 @@
           <t>autumnal generative synth with midi and crow sequencing</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Gud-dWz-etE</t>
+        </is>
+      </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/fall-generative-synth-sequencer/48991</t>
@@ -5017,7 +5391,11 @@
           <t>i will show you fear in a handful of dust</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Al0yMoDzCQY</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/fiahod</t>
@@ -5067,7 +5445,11 @@
           <t>a sequencer that travels through numbers and time</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HD4Mtnaj3oE</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/fibonacci/54153</t>
@@ -5113,7 +5495,11 @@
           <t>a fixed filter bank</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/uploads/default/original/3X/2/f/2f12a0d24609c87f0f1aa22ffc93e992e17e66c8.mp3</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/fixed-filter-banking-crisis/71735</t>
@@ -5163,7 +5549,11 @@
           <t>l-systems sequencer and bandpass-filtered sawtooth engine</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/496481575</t>
+        </is>
+      </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/40261</t>
@@ -5213,7 +5603,11 @@
           <t>polyphonic 6 operator fm synth</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HI9B-vuWF4A</t>
+        </is>
+      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21395</t>
@@ -5276,7 +5670,11 @@
           <t>https://norns.community/folio/</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
           <t>2021-09-05</t>
@@ -5305,7 +5703,11 @@
           <t>my pal</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ubLWJrVj3LI?si=TeVwXzhjD5WzUFAZ</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/foot-foot/73334</t>
@@ -5355,7 +5757,11 @@
           <t>a playable  oscilloscope for norns and crow</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-pqok4cqr6Q</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/forge/65656</t>
@@ -5418,7 +5824,11 @@
           <t>https://norns.community/formmatter/</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
           <t>2026-02-26</t>
@@ -5447,7 +5857,11 @@
           <t>euclidean rhythms with logic and probability</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bv5VRKclkMB/</t>
+        </is>
+      </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/foulplay/21081</t>
@@ -5514,7 +5928,11 @@
           <t>https://norns.community/foundry/</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
           <t>2020-10-09</t>
@@ -5543,7 +5961,11 @@
           <t>fugu meets awake sequencer</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ng1WMOX9FtI</t>
+        </is>
+      </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/fugarc/34446</t>
@@ -5589,7 +6011,11 @@
           <t>multi playhead sequencer</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EcH1FbNQ16g</t>
+        </is>
+      </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21033</t>
@@ -5635,7 +6061,11 @@
           <t>organized electricty with norns &amp; crow</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uuIhcHvodu4</t>
+        </is>
+      </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/gematria</t>
@@ -5685,7 +6115,11 @@
           <t>twin granulators. watch them race.</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BwOp6t1FVeX/</t>
+        </is>
+      </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/gemini/21086</t>
@@ -5731,7 +6165,11 @@
           <t>your norns plays Terry Riley's In C</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hLFo0XP8N3s</t>
+        </is>
+      </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/get-in-the-sea/45729</t>
@@ -5794,7 +6232,11 @@
           <t>https://norns.community/giro/</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
           <t>2023-12-19</t>
@@ -5823,7 +6265,11 @@
           <t>extreme sound stretcher and harmoniser</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr"/>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QspuCt1FM9M</t>
+        </is>
+      </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/glaciers/45117</t>
@@ -5869,7 +6315,11 @@
           <t>lets glitch with glitchlets.</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=h7p3H9pbdR8</t>
+        </is>
+      </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/glitchlets/37069</t>
@@ -5915,7 +6365,11 @@
           <t>5 unsynchronized loops with an auto mode</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr"/>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LItXkRNhBM4</t>
+        </is>
+      </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/glitch-looper/54014</t>
@@ -5965,7 +6419,11 @@
           <t>granular synth inspired by mlr/rove, grainfields 20 and loomer cumulus</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr"/>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Cc2ZtBWfH3k</t>
+        </is>
+      </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/glut/21175</t>
@@ -6011,7 +6469,11 @@
           <t>entropic background radiation</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr"/>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wXzy9Ky52nA</t>
+        </is>
+      </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/goldeneye</t>
@@ -6061,7 +6523,11 @@
           <t>three lands with six grains</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr"/>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=npnsrLpwAXM</t>
+        </is>
+      </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/graintopia/62343</t>
@@ -6107,7 +6573,11 @@
           <t>quantized granular sequencer</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/576432638</t>
+        </is>
+      </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/granchild/41894</t>
@@ -6153,7 +6623,11 @@
           <t>a model of sonic behaviour</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bW1otBbTh-E</t>
+        </is>
+      </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/grd/33768</t>
@@ -6199,7 +6673,11 @@
           <t>simple drone synth, grendel drone commander inspired</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr"/>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/809326801</t>
+        </is>
+      </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/31721</t>
@@ -6245,7 +6723,11 @@
           <t>echo / delay</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B6Ckm_-B2qp/</t>
+        </is>
+      </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/greyhole/27687</t>
@@ -6295,7 +6777,11 @@
           <t>A utility script for testing grids</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr"/>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B8aiA-NBYqJ/</t>
+        </is>
+      </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/grid-test/29346</t>
@@ -6341,7 +6827,11 @@
           <t>sixteen notes, seven timbres</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr"/>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oZ8iEdrWWwE</t>
+        </is>
+      </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/52122</t>
@@ -6387,7 +6877,11 @@
           <t>A Karper-esque take on Duncan Geere's gridofpoints</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr"/>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C0T0mrXNH9i</t>
+        </is>
+      </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/gridofrings/65138</t>
@@ -6437,7 +6931,11 @@
           <t>16 track isomorphic grid sequencer for timber and midi</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr"/>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RaOxDwYcZiQ</t>
+        </is>
+      </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/38559</t>
@@ -6487,7 +6985,11 @@
           <t>physics based sequencer for people who like cats</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr"/>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ip6Ou3-8g_s</t>
+        </is>
+      </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/46075</t>
@@ -6600,7 +7102,11 @@
           <t>https://norns.community/hachi/</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
           <t>2020-12-20</t>
@@ -6629,7 +7135,11 @@
           <t>a safe space?</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr"/>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1mEBZmao-uc</t>
+        </is>
+      </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/haven/21285</t>
@@ -6679,7 +7189,11 @@
           <t>four track live granular looper</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/513390690</t>
+        </is>
+      </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/haze/41781</t>
@@ -6725,7 +7239,11 @@
           <t>the sound begins here but you began there</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr"/>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ue4eXW6ywDM</t>
+        </is>
+      </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/here-there/36170</t>
@@ -6771,7 +7289,11 @@
           <t>demo scripts for hid functionality</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bt4tU6RlVME/</t>
+        </is>
+      </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/hid-demo/21315</t>
@@ -6838,7 +7360,11 @@
           <t>https://norns.community/hpns/</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
           <t>2020-05-30</t>
@@ -6867,7 +7393,11 @@
           <t>Bass and lead voice with a multi-playhead sequencer.</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/uploads/default/original/3X/2/e/2e768ee314063d64a4aa87191617d57ca8d13825.mp3</t>
+        </is>
+      </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/hs010-happy-synthesis-010</t>
@@ -6959,7 +7489,11 @@
           <t>supersaw synth with feedback</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr"/>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DjVB6LhSrNg</t>
+        </is>
+      </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/icarus/43271</t>
@@ -7026,7 +7560,11 @@
           <t>https://norns.community/iiitoii/</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
@@ -7055,7 +7593,11 @@
           <t>drum machine based on arturia's drumbrute impact</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr"/>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NQg1-Sljvro</t>
+        </is>
+      </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/impact/45247</t>
@@ -7101,7 +7643,11 @@
           <t>2-dimensional polyrythmic, random note sequencer.</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr"/>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/977550862</t>
+        </is>
+      </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/initenere/41193</t>
@@ -7151,7 +7697,11 @@
           <t>a live-coding environment</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr"/>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/590312883</t>
+        </is>
+      </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/internorns/46565</t>
@@ -7214,7 +7764,11 @@
           <t>https://norns.community/interpret/</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
           <t>2023-07-29</t>
@@ -7264,7 +7818,11 @@
           <t>https://norns.community/intervaltrainer/</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
           <t>2023-02-11</t>
@@ -7293,7 +7851,11 @@
           <t>fm7, earthsea, kria, looper</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr"/>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B904ErwBlfy/</t>
+        </is>
+      </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/islands-0-1/30234</t>
@@ -7339,7 +7901,11 @@
           <t>isomorphic sequencer for norns and grid</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr"/>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/328649268</t>
+        </is>
+      </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/isoseq/21026</t>
@@ -7385,7 +7951,11 @@
           <t>ambient random sequencer</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I1eDFzpWfJc</t>
+        </is>
+      </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/jala/41788</t>
@@ -7431,7 +8001,11 @@
           <t>16 second looper</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tv/CcQX_XQAwSR</t>
+        </is>
+      </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/jiffy/25475</t>
@@ -7498,7 +8072,11 @@
           <t>https://norns.community/just-play/</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
           <t>2025-01-14</t>
@@ -7527,7 +8105,11 @@
           <t>subharmonic sequencer for jf</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fv-vg-ipDS4</t>
+        </is>
+      </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/justharmonicon</t>
@@ -7577,7 +8159,11 @@
           <t>grid-based sample sequencer</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/510535132</t>
+        </is>
+      </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/kolor/40504</t>
@@ -7640,7 +8226,11 @@
           <t>https://norns.community/kreislauf/</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
           <t>2022-01-15</t>
@@ -7669,7 +8259,11 @@
           <t>port of kria from ansible</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FtyTv8ngdI4</t>
+        </is>
+      </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21255</t>
@@ -7715,7 +8309,11 @@
           <t>a Lorenz system sequencer and mod matrix with a physical modelling synthesis engine</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr"/>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/48382205</t>
+        </is>
+      </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/54975</t>
@@ -7761,7 +8359,11 @@
           <t>interact with a musical emission spectrum</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr"/>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/CiAa3vLO6JE</t>
+        </is>
+      </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/l-ll-l/58123</t>
@@ -7807,7 +8409,11 @@
           <t>a music box inspired generative instrument/sequencer</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr"/>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z61m8jPcQTA</t>
+        </is>
+      </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/lamellae/69409</t>
@@ -7853,7 +8459,11 @@
           <t>substitution sequencer</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr"/>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=V_N9VvBVABU</t>
+        </is>
+      </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/lamination/58652</t>
@@ -7903,7 +8513,11 @@
           <t>looper/delay</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr"/>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CJlvQzxBYTW/</t>
+        </is>
+      </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/larc/39790</t>
@@ -7970,7 +8584,11 @@
           <t>https://norns.community/lemniscate/</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
           <t>2024-05-19</t>
@@ -7999,7 +8617,11 @@
           <t>1d cellular automata sequencer</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr"/>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7L1dpMnmMbA</t>
+        </is>
+      </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/less-concepts-norns</t>
@@ -8049,7 +8671,11 @@
           <t>seeding fields forever</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr"/>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYI71UKiuu8</t>
+        </is>
+      </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/lissadron/32509</t>
@@ -8099,7 +8725,11 @@
           <t>pattern weaving sequencer for grids</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr"/>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BoXcWG5AFrw</t>
+        </is>
+      </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/loom/21091</t>
@@ -8145,7 +8775,11 @@
           <t>strange attractors for crow</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr"/>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/uploads/default/original/3X/e/c/ec3bb113e4784b9ee27220ebef33a547d1101ce4.mp3</t>
+        </is>
+      </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/71465</t>
@@ -8195,7 +8829,11 @@
           <t>an electroacoustic drumset and sequencer</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr"/>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/674023534</t>
+        </is>
+      </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/lorenzos-drums/52549</t>
@@ -8241,7 +8879,11 @@
           <t>data sonification for norns</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr"/>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9N2OP0T_qRc</t>
+        </is>
+      </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/loud-numbers-data-sonification-with-norns/51353</t>
@@ -8333,7 +8975,11 @@
           <t>a sequencer based on the RYK M-185</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr"/>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aaKB7Us2Vl8</t>
+        </is>
+      </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/m18s-now-for-norns/32068</t>
@@ -8379,7 +9025,11 @@
           <t>signal routing and modulated note echo for midi and cv</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr"/>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/uploads/default/original/3X/b/6/b6fbe484216f273d02db5a433fc7f87370597132.mp3</t>
+        </is>
+      </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/magpie/67460</t>
@@ -8425,7 +9075,11 @@
           <t>make breakbeats from samples</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr"/>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/684681570</t>
+        </is>
+      </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/makebreakbeat/53301</t>
@@ -8471,7 +9125,11 @@
           <t>a 7 track granular sample player</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr"/>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bv0HMXEghpd/?utm_source=ig_share_sheet&amp;igshid=uhwqp6cm7654</t>
+        </is>
+      </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21066</t>
@@ -8521,7 +9179,11 @@
           <t>multi-effects processing for live performance</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr"/>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bw9I_tjoHUg/?utm_source=ig_web_button_share_sheet</t>
+        </is>
+      </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/manifold/22098</t>
@@ -8567,7 +9229,11 @@
           <t>spatial sequencer with cats</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr"/>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=riol61rH76A</t>
+        </is>
+      </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/marcovaldo/66119</t>
@@ -8613,7 +9279,11 @@
           <t>8 band resonator</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr"/>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/532952102</t>
+        </is>
+      </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/massif/</t>
@@ -8663,7 +9333,11 @@
           <t>grid-enabled rhizomatic cascading counter</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr"/>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/146731772</t>
+        </is>
+      </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21185</t>
@@ -8768,7 +9442,11 @@
           <t>https://norns.community/metronome/</t>
         </is>
       </c>
-      <c r="J175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
           <t>2025-09-21</t>
@@ -8797,7 +9475,11 @@
           <t>A MIDI monitor for norns</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr"/>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-zXIbLDpzAo</t>
+        </is>
+      </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/midi-monitor/35036</t>
@@ -8860,7 +9542,11 @@
           <t>https://norns.community/midi-review/</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
           <t>2023-01-13</t>
@@ -8889,7 +9575,11 @@
           <t>midi cc looper mod</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr"/>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_Mm79ezd1Oc</t>
+        </is>
+      </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/midididi-midi-cc-looper-mod/67129</t>
@@ -8935,7 +9625,11 @@
           <t>Use launchpads and other midi grid devices w/ Norns</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr"/>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zfe3ajpISiY</t>
+        </is>
+      </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/42336</t>
@@ -9006,7 +9700,11 @@
           <t>https://norns.community/midiplayer/</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
@@ -9035,7 +9733,11 @@
           <t>live sample-cutting platform</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr"/>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/266741634</t>
+        </is>
+      </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21145</t>
@@ -9081,7 +9783,11 @@
           <t>extended version of mlr</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr"/>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_0ur71EtL14</t>
+        </is>
+      </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mlre/57371</t>
@@ -9131,7 +9837,11 @@
           <t>classic polysynth with solar system patch creator</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr"/>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BoXJavpAE3R/</t>
+        </is>
+      </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/molly-the-poly/21090</t>
@@ -9194,7 +9904,11 @@
           <t>https://norns.community/moln/</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
           <t>2022-03-07</t>
@@ -9223,7 +9937,11 @@
           <t>small kit of midi utilities to transpose and route midi messages</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr"/>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g_joxEeB3ss</t>
+        </is>
+      </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/23273</t>
@@ -9269,7 +9987,11 @@
           <t>A mod to toggle stereo and mono input</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr"/>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/54S5h1Zktaw</t>
+        </is>
+      </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/monomaniac-a-mod-to-toggle-stereo-and-mono-input/63892</t>
@@ -9319,7 +10041,11 @@
           <t>explore a galaxy of rhythm</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr"/>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/665856265</t>
+        </is>
+      </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/moonraker/51803</t>
@@ -9365,7 +10091,11 @@
           <t>enabling you to craft complex rhythms and harmonies effortlessly</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr"/>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J1ckUZvhFJ0</t>
+        </is>
+      </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mosaic/69304</t>
@@ -9411,7 +10141,11 @@
           <t>sound maker and sequencer heavily inspired by Laurie Spiegel's Music Mouse</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr"/>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>https://w.soundcloud.com/player/?visual=false&amp;url=https%3A%2F%2Fapi.soundcloud.com%2Ftracks%2F983475475&amp;show_artwork=true&amp;maxheight=166</t>
+        </is>
+      </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mouse/41562</t>
@@ -9457,7 +10191,11 @@
           <t>like mr.radar or mr.coffee but for samples</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr"/>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/509450523</t>
+        </is>
+      </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mx-samples/41400</t>
@@ -9503,7 +10241,11 @@
           <t>like mr.radar or mr.coffee but for synths</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr"/>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/640394839</t>
+        </is>
+      </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/mx-synths/49535</t>
@@ -9549,7 +10291,11 @@
           <t>native norns Kria</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr"/>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BPWFcgadT50&amp;t=483s</t>
+        </is>
+      </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/n-kria-0-13-native-norns-kria/60403</t>
@@ -9616,7 +10362,11 @@
           <t>https://norns.community/n16o/</t>
         </is>
       </c>
-      <c r="J193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
           <t>2020-01-04</t>
@@ -9645,7 +10395,11 @@
           <t>A Norns granular synthesizer, inspired by solar system.</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr"/>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YAenlbawxLE</t>
+        </is>
+      </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nameless-nightmare/68145</t>
@@ -9691,7 +10445,11 @@
           <t>norns mod that turns crow into a synth using nb</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr"/>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DU_R516qjAc</t>
+        </is>
+      </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nb-drumcrow-norns-mod-that-turns-crow-into-a-4-voice-synth/69066</t>
@@ -9737,7 +10495,11 @@
           <t>mx.synths as an nb player</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr"/>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nza0k0ZhVIo</t>
+        </is>
+      </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/n-b-et-al-v0-1/60374/324?u=sonocircuit</t>
@@ -9783,7 +10545,11 @@
           <t>a norns classic as nb player</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr"/>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nza0k0ZhVIo</t>
+        </is>
+      </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/n-b-et-al-v0-1/60374/324?u=sonocircuit</t>
@@ -9829,7 +10595,11 @@
           <t>sample playback as an nb player</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr"/>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nza0k0ZhVIo</t>
+        </is>
+      </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/n-b-et-al-v0-1/60374/324?u=sonocircuit</t>
@@ -9875,7 +10645,11 @@
           <t>norns/circle/01 drone in three worlds</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sjv_m370hyw</t>
+        </is>
+      </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-circle-01-drone-in-three-worlds/28582</t>
@@ -9921,7 +10695,11 @@
           <t>norns/circle/02 rhythm and sound</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr"/>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/416730766</t>
+        </is>
+      </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-circle-02-rhythm-and-sound/31645</t>
@@ -9967,7 +10745,11 @@
           <t>norns/circle/03 dressed in sequins</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr"/>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/sound-and-process/scarlet</t>
+        </is>
+      </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-circle-03-dressed-in-sequins/57649</t>
@@ -10013,7 +10795,11 @@
           <t>4-track modeless tape looper, delay, &amp; sampler</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr"/>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tXT2iarlvHI</t>
+        </is>
+      </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/ndls/</t>
@@ -10080,7 +10866,11 @@
           <t>https://norns.community/nice-tapes/</t>
         </is>
       </c>
-      <c r="J203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
           <t>2022-08-11</t>
@@ -10109,7 +10899,11 @@
           <t>scheme dialect livecoding tracker for norns</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr"/>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B54rUM6hnWJ/</t>
+        </is>
+      </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nisp/27596</t>
@@ -10155,7 +10949,11 @@
           <t>a port of ken stone's infinite melody and modulo magic cgs serge modules</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr"/>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0d8qU9nQ8To</t>
+        </is>
+      </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nmmelodymagic/</t>
@@ -10218,7 +11016,11 @@
           <t>https://norns.community/nmQuadroDubber/</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
           <t>2021-05-01</t>
@@ -10247,7 +11049,11 @@
           <t>a weird stereo delay effect for external audio</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr"/>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6-mCpgKhsQo</t>
+        </is>
+      </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nmrain/</t>
@@ -10293,7 +11099,11 @@
           <t>deform external audio with math and impress your nerd friends</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr"/>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/COX5xp6hYkh</t>
+        </is>
+      </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nmsmartypants/</t>
@@ -10339,7 +11149,11 @@
           <t>noize is a little synth to make some noise - simple as that!</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr"/>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bCr1xxfevpc</t>
+        </is>
+      </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/noize/61967</t>
@@ -10389,7 +11203,11 @@
           <t>Four oscillators, six algorithms to mix and mangle.</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr"/>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bCr1xxfevpc</t>
+        </is>
+      </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/noizeop/61966</t>
@@ -10456,7 +11274,11 @@
           <t>https://norns.community/norman/</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
           <t>2019-05-19</t>
@@ -10485,7 +11307,11 @@
           <t>remotely control norns from the browser</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr"/>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/484176216</t>
+        </is>
+      </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-online/38547</t>
@@ -10573,7 +11399,11 @@
           <t>beat-synced looper, slicer, and sequencer</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr"/>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XldC1KqaD_Y</t>
+        </is>
+      </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nydl/51886</t>
@@ -10661,7 +11491,11 @@
           <t>connect-the-dots sequencer w/ fm synthesizer</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr"/>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/638838322</t>
+        </is>
+      </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/o-o-o</t>
@@ -10724,7 +11558,11 @@
           <t>https://norns.community/oblique/</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
           <t>2021-11-30</t>
@@ -10753,7 +11591,11 @@
           <t>monophonic digital-style percussion voice</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr"/>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>https://zbs.fm/audio/2023-01-25%20oilcan-demos.mp3</t>
+        </is>
+      </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/oilcan-percussion-co/60754</t>
@@ -10803,7 +11645,11 @@
           <t>minimal manual controller script</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr"/>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oBKVeXLxXF4</t>
+        </is>
+      </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/onehanded/25869</t>
@@ -10849,7 +11695,11 @@
           <t>ocean noise generator</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr"/>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2V-r5gyqzv4</t>
+        </is>
+      </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/ong-ocean-noise-generator-for-monome-norns/50364/3</t>
@@ -10895,7 +11745,11 @@
           <t>digital tape loops, x 6</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr"/>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/659711272</t>
+        </is>
+      </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/oooooo</t>
@@ -10958,7 +11812,11 @@
           <t>https://norns.community/orbital/</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
           <t>2019-04-15</t>
@@ -10987,7 +11845,11 @@
           <t>visual programming language, designed to create procedural sequencers on the fly</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr"/>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BxRUGzlFqEX/</t>
+        </is>
+      </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/22492</t>
@@ -11037,7 +11899,11 @@
           <t xml:space="preserve"> 3-operator FM synth + fx for norns </t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr"/>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ug39z2mZhsQ</t>
+        </is>
+      </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/orgn/</t>
@@ -11087,7 +11953,11 @@
           <t>orgn + wrms</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr"/>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6z_dkUMtJPQ</t>
+        </is>
+      </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/orgn/</t>
@@ -11137,7 +12007,11 @@
           <t>Sort of Radio music clone where each audio file in tape folder is a station</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr"/>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/494471477</t>
+        </is>
+      </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/ortf/39694</t>
@@ -11183,7 +12057,11 @@
           <t>dual tape delay/looper/sampler</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr"/>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/333979510</t>
+        </is>
+      </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/22149</t>
@@ -11233,7 +12111,11 @@
           <t>a synth based on additive synthesis</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr"/>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/NA8ZCD6Anpc?si=DZfQl6ETRvHqEAdh</t>
+        </is>
+      </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/overtones/72641</t>
@@ -11283,7 +12165,11 @@
           <t>Bird migration patterns as sound</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr"/>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g2vcoW4MjbI</t>
+        </is>
+      </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/overwintering/58444</t>
@@ -11350,7 +12236,11 @@
           <t>https://norns.community/p8/</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr"/>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
           <t>2022-01-12</t>
@@ -11379,7 +12269,11 @@
           <t>sampler + tracker to construct imaginary worlds</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr"/>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fKxxuXu5fC8&amp;t=1642s</t>
+        </is>
+      </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/paracosms/57350</t>
@@ -11429,7 +12323,11 @@
           <t>paranibbles for paradiddles</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr"/>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EZBpxkxJg0o</t>
+        </is>
+      </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/paranibbles/68052/</t>
@@ -11496,7 +12394,11 @@
           <t>https://norns.community/parrot/</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
           <t>2023-05-16</t>
@@ -11525,7 +12427,11 @@
           <t>west coast style mono synth</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr"/>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bl1VFffnz7w/</t>
+        </is>
+      </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/passersby/21089</t>
@@ -11571,7 +12477,11 @@
           <t>midi passthrough library with examples</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr"/>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CQbfLPthItd/</t>
+        </is>
+      </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/passthrough/31156</t>
@@ -11621,7 +12531,11 @@
           <t>dual function sequencer for monome norns, crow and grid</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr"/>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/creurer/patchwork-21</t>
+        </is>
+      </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/patchwork/28800</t>
@@ -11667,7 +12581,11 @@
           <t>A movement recorder for norns and crow</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr"/>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XNfEkUwsCK8</t>
+        </is>
+      </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/path-trace-movement-recorder-for-norns-and-crow/66276</t>
@@ -11713,7 +12631,11 @@
           <t>chainable effects for live performance</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr"/>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/itwasthewires/060820002-0coast-0ctrl-norns</t>
+        </is>
+      </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/31119</t>
@@ -11763,7 +12685,11 @@
           <t>livecoding environment</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr"/>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QcNEq_dyiuo</t>
+        </is>
+      </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/49564</t>
@@ -11813,7 +12739,11 @@
           <t>a digitally modeled analog filter</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr"/>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/381676550</t>
+        </is>
+      </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/27988</t>
@@ -11863,7 +12793,11 @@
           <t>community radio for monome norns...yar</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr"/>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=voc-Hp14yOg</t>
+        </is>
+      </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/pirate-radio/49013</t>
@@ -11913,7 +12847,11 @@
           <t>snake game inspired sequencer for norns</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr"/>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hMjUklY1JYU</t>
+        </is>
+      </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/pit-orchisstra/66521</t>
@@ -11963,7 +12901,11 @@
           <t>microtonal scale explorer / arpeggiator / grid keyboard</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr"/>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/474036472</t>
+        </is>
+      </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/pitfalls/37795</t>
@@ -12009,7 +12951,11 @@
           <t>sequencer and sampler player based around the OP-1 'pattern' sequencer</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr"/>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hab3Xm-OJGM</t>
+        </is>
+      </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/pitter-patter/68944</t>
@@ -12059,7 +13005,11 @@
           <t>a sampler that works in realtime</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr"/>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CFla2iJh9zC</t>
+        </is>
+      </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/piwip/36642</t>
@@ -12105,7 +13055,11 @@
           <t>generative visual sequencer instrument</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr"/>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=epAPl9S3TWo</t>
+        </is>
+      </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/pixels/38762</t>
@@ -12151,7 +13105,11 @@
           <t>function animator</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr"/>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=90DyLOnhFJ8</t>
+        </is>
+      </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/plasma/64038</t>
@@ -12197,7 +13155,11 @@
           <t>string-like keyboard and sequencer</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr"/>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/520650445</t>
+        </is>
+      </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/plonky/42520</t>
@@ -12243,7 +13205,11 @@
           <t>a shimmery reverb</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr"/>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/383786715</t>
+        </is>
+      </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/28320</t>
@@ -12293,7 +13259,11 @@
           <t>sampler for arc and norns</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr"/>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y5IK7cSAQJ8</t>
+        </is>
+      </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/postskript</t>
@@ -12356,7 +13326,11 @@
           <t>https://norns.community/ppm_norns/</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr"/>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
           <t>2023-05-21</t>
@@ -12385,7 +13359,11 @@
           <t>an experimental sequencer that works a bit like the classic punchcard computer</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr"/>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jZUtkNuEDqY</t>
+        </is>
+      </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/23557</t>
@@ -12431,7 +13409,11 @@
           <t>A brute-force password hack inspired sequencer.</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr"/>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/shorts/JbNxznmMTfk</t>
+        </is>
+      </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/qfwfq</t>
@@ -12477,7 +13459,11 @@
           <t>probabilistic 4-track sequencer</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr"/>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CVbdWnWA9UM</t>
+        </is>
+      </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/quence/29436</t>
@@ -12565,7 +13551,11 @@
           <t>a five-piece orchestra sequence synthesizer</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr"/>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p_OTXsPqMhU</t>
+        </is>
+      </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/rachim/66632</t>
@@ -12632,7 +13622,11 @@
           <t>https://norns.community/raft/</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr"/>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
           <t>2022-05-24</t>
@@ -12661,7 +13655,11 @@
           <t>generative melodies complete with lo-fi effects</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr"/>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DD7XTDHkd2s</t>
+        </is>
+      </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/raindrops-simple-generative-synth-sequencer/47633</t>
@@ -12711,7 +13709,11 @@
           <t>Randomizer for Dreadbox Typhon</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr"/>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hD-t4onIJbk</t>
+        </is>
+      </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/randomizer-typhon/54196</t>
@@ -12757,7 +13759,11 @@
           <t>arc based granular four track sampler with live recording and friction.</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr"/>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/545457820</t>
+        </is>
+      </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/rangl/44673</t>
@@ -12803,7 +13809,11 @@
           <t>a kinetic sequencer</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr"/>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BmSiQgrAhRg/</t>
+        </is>
+      </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/23243</t>
@@ -12849,7 +13859,11 @@
           <t>a 4-track asynchronous looper, inspired by op-1 tape recorder and mannequins w/ eurorack module.</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr"/>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3XKruCUB1PM</t>
+        </is>
+      </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21030</t>
@@ -12941,7 +13955,11 @@
           <t>mash of REPL and looper; a live performance code sequencer</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr"/>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FPE5DOlScIY</t>
+        </is>
+      </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/51485</t>
@@ -12987,7 +14005,11 @@
           <t>folded euclidean arpeggiator</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr"/>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1099770303</t>
+        </is>
+      </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/ribbons/72521</t>
@@ -13033,7 +14055,11 @@
           <t>varispeed multitap echo</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr"/>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AUcsdTWoAys</t>
+        </is>
+      </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/rpls/</t>
@@ -13083,7 +14109,11 @@
           <t>record a sound an play it back at various RPM ratios</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr"/>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=K7_9-ymumd4</t>
+        </is>
+      </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/38542</t>
@@ -13133,7 +14163,11 @@
           <t>an 8 voice lofi percussion synthesizer and sequencer</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr"/>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hvPSVOyGsYg</t>
+        </is>
+      </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/31828</t>
@@ -13200,7 +14234,11 @@
           <t>https://norns.community/sam/</t>
         </is>
       </c>
-      <c r="J269" s="2" t="inlineStr"/>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
           <t>2022-10-14</t>
@@ -13229,7 +14267,11 @@
           <t>swap samples within loops</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr"/>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/688648344</t>
+        </is>
+      </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/sampswap/53719</t>
@@ -13275,7 +14317,11 @@
           <t>a minimalist clock-synced looper</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr"/>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vkt7b72l1Cg</t>
+        </is>
+      </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/34095</t>
@@ -13325,7 +14371,11 @@
           <t>3 voice looper based on samsara</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr"/>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/c6nqTYF_J-k</t>
+        </is>
+      </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/samthree-three-voice-pitched-looper/60482</t>
@@ -13375,7 +14425,11 @@
           <t>a poetry sequencer</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr"/>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ngVAAIWE_Io</t>
+        </is>
+      </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/schicksalslied/59227</t>
@@ -13421,7 +14475,11 @@
           <t>multitrack polyrhythmic sequencer</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr"/>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vvl44pg3hMM</t>
+        </is>
+      </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/scholastic-multitrack-polyrhythmic-sequencer/64232</t>
@@ -13467,7 +14525,11 @@
           <t>scrying stone for monome norns</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr"/>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_go_5QtmvL8</t>
+        </is>
+      </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/scryingstone-norns/70778</t>
@@ -13534,7 +14596,11 @@
           <t>https://norns.community/seaflex/</t>
         </is>
       </c>
-      <c r="J276" s="2" t="inlineStr"/>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
           <t>2023-12-29</t>
@@ -13622,7 +14688,11 @@
           <t>https://norns.community/semiconductor/</t>
         </is>
       </c>
-      <c r="J278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
     </row>
@@ -13647,7 +14717,11 @@
           <t>continuous dynamic melody sequencer for 16n+grid</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr"/>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ylj5nLv6IEg</t>
+        </is>
+      </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/54492</t>
@@ -13693,7 +14767,11 @@
           <t>Explore serialism in the spirit of Arnold Schönberg and others</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr"/>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8sm3o-2cfIQ</t>
+        </is>
+      </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/serialism/68332</t>
@@ -13743,7 +14821,11 @@
           <t>visuals-based modulation source for crow and midi</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr"/>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8TD0vDnNUYc</t>
+        </is>
+      </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/36759</t>
@@ -13789,7 +14871,11 @@
           <t>random sequencer for norns, crow, and grid</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr"/>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B3kCWYtBl_8/</t>
+        </is>
+      </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/26221</t>
@@ -13835,7 +14921,11 @@
           <t>fork of schicksalslied for use with shbobo shnth</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr"/>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T5zg_Nl8zuI</t>
+        </is>
+      </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/shnthsalslied/59232</t>
@@ -13881,7 +14971,11 @@
           <t>a thunderstorm for norns</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr"/>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/885593155</t>
+        </is>
+      </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/31622</t>
@@ -13931,7 +15025,11 @@
           <t>a creative canvas for a sidecar grid</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr"/>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFfKduXWIq4</t>
+        </is>
+      </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/sidvagn/72514</t>
@@ -13981,7 +15079,11 @@
           <t>live grains</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr"/>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/user-136434953/silos-2</t>
+        </is>
+      </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/43804</t>
@@ -14031,7 +15133,11 @@
           <t>16 sine waves</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr"/>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b8WXjrjjRe8</t>
+        </is>
+      </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/39292</t>
@@ -14077,7 +15183,11 @@
           <t>a sequencer inspired on the M185/Intellijel Metropolis</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr"/>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CH8dDmShk9Z/</t>
+        </is>
+      </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/skylines/38856</t>
@@ -14123,7 +15233,11 @@
           <t>sequencer for apes</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr"/>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=G8dZLtmcJ60</t>
+        </is>
+      </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/smash/48782</t>
@@ -14215,7 +15329,11 @@
           <t>sequencer</t>
         </is>
       </c>
-      <c r="E291" s="2" t="inlineStr"/>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5-2XTOoBuU0</t>
+        </is>
+      </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/spirals/40678</t>
@@ -14265,7 +15383,11 @@
           <t>an eduscript for sequins and lattice</t>
         </is>
       </c>
-      <c r="E292" s="2" t="inlineStr"/>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kaH6qetN0fE</t>
+        </is>
+      </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/splicer</t>
@@ -14315,7 +15437,11 @@
           <t>an amplitude and frequency tracking effects processor/sampler/sequencer</t>
         </is>
       </c>
-      <c r="E293" s="2" t="inlineStr"/>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/660537339</t>
+        </is>
+      </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/51191</t>
@@ -14361,7 +15487,11 @@
           <t>a stack of 8 fixed-frequency resonant bandpass filters</t>
         </is>
       </c>
-      <c r="E294" s="2" t="inlineStr"/>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zp7DKJaQs9o</t>
+        </is>
+      </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/35218</t>
@@ -14407,7 +15537,11 @@
           <t>a simple step sequencer</t>
         </is>
       </c>
-      <c r="E295" s="2" t="inlineStr"/>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pI81ISvjST4</t>
+        </is>
+      </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/step/21093</t>
@@ -14453,7 +15587,11 @@
           <t>drone inspired by Moffenzeef Stargazer</t>
         </is>
       </c>
-      <c r="E296" s="2" t="inlineStr"/>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iaO3x2EGuU0</t>
+        </is>
+      </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/33889</t>
@@ -14499,7 +15637,11 @@
           <t>a multi play head sequencer</t>
         </is>
       </c>
-      <c r="E297" s="2" t="inlineStr"/>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pTOR4oDJ6hE</t>
+        </is>
+      </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/streams/61436</t>
@@ -14549,7 +15691,11 @@
           <t>a collection of pattern recorders</t>
         </is>
       </c>
-      <c r="E298" s="2" t="inlineStr"/>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/328470668</t>
+        </is>
+      </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21101</t>
@@ -14595,7 +15741,11 @@
           <t>a plucky little pattern sequencer</t>
         </is>
       </c>
-      <c r="E299" s="2" t="inlineStr"/>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/328638255</t>
+        </is>
+      </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21025</t>
@@ -14641,7 +15791,11 @@
           <t>a clocked, three-track stereo audio mangler</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr"/>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HgFYZcr8_xY</t>
+        </is>
+      </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/stwnsh/69125</t>
@@ -14708,7 +15862,11 @@
           <t>https://norns.community/stv/</t>
         </is>
       </c>
-      <c r="J301" s="2" t="inlineStr"/>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
           <t>2025-11-20</t>
@@ -14737,7 +15895,11 @@
           <t>a noise synth for norns</t>
         </is>
       </c>
-      <c r="E302" s="2" t="inlineStr"/>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZayWqvTqd_o</t>
+        </is>
+      </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/stoy/67054</t>
@@ -14783,7 +15945,11 @@
           <t>an introspective drum machine</t>
         </is>
       </c>
-      <c r="E303" s="2" t="inlineStr"/>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/557258118</t>
+        </is>
+      </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/supertonic/45551</t>
@@ -14829,7 +15995,11 @@
           <t>analysis-driven live audio processing</t>
         </is>
       </c>
-      <c r="E304" s="2" t="inlineStr"/>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5IPCUoO0vYg</t>
+        </is>
+      </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/sway/21117</t>
@@ -14892,7 +16062,11 @@
           <t>https://norns.community/sweetbees/</t>
         </is>
       </c>
-      <c r="J305" s="2" t="inlineStr"/>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
           <t>2021-11-08</t>
@@ -14921,7 +16095,11 @@
           <t>a synthesizer critter</t>
         </is>
       </c>
-      <c r="E306" s="2" t="inlineStr"/>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/593857252</t>
+        </is>
+      </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/synthy/48062</t>
@@ -14957,15 +16135,17 @@
           <t>its_your_bedtime</t>
         </is>
       </c>
-      <c r="C307" s="2" t="n">
-        <v/>
-      </c>
+      <c r="C307" s="2" t="inlineStr"/>
       <c r="D307" s="2" t="inlineStr">
         <is>
           <t>parameter locking step sequencer</t>
         </is>
       </c>
-      <c r="E307" s="2" t="inlineStr"/>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Brm-za6FWMZ/</t>
+        </is>
+      </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/takt/21032</t>
@@ -15011,7 +16191,11 @@
           <t>bending rhythmic arpeggio</t>
         </is>
       </c>
-      <c r="E308" s="2" t="inlineStr"/>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T9nk9IomwYM</t>
+        </is>
+      </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/37965</t>
@@ -15061,7 +16245,11 @@
           <t>live tape deck emulation (saturation, distortion, wow/flutter)</t>
         </is>
       </c>
-      <c r="E309" s="2" t="inlineStr"/>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/666500841</t>
+        </is>
+      </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tapedeck/51919</t>
@@ -15107,7 +16295,11 @@
           <t>Bird song, and lots of it. And pics, too.</t>
         </is>
       </c>
-      <c r="E310" s="2" t="inlineStr"/>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yvc-pNiVl_c</t>
+        </is>
+      </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/69028</t>
@@ -15157,7 +16349,11 @@
           <t>use the grid to create, perform and sequence sound objects</t>
         </is>
       </c>
-      <c r="E311" s="2" t="inlineStr"/>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M0aHRQAvBRA</t>
+        </is>
+      </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tetra/68343</t>
@@ -15203,7 +16399,11 @@
           <t>triangle wave organ with variable slope for norns &amp; shbobo shnth</t>
         </is>
       </c>
-      <c r="E312" s="2" t="inlineStr"/>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/1391254177</t>
+        </is>
+      </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tetrabobo/60112</t>
@@ -15249,7 +16449,11 @@
           <t>tetrabobo + otis = tetrabotis</t>
         </is>
       </c>
-      <c r="E313" s="2" t="inlineStr"/>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wqTQ7xwg5CI</t>
+        </is>
+      </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tetrabotis/60216</t>
@@ -15295,7 +16499,11 @@
           <t>one-shot synthesis engine</t>
         </is>
       </c>
-      <c r="E314" s="2" t="inlineStr"/>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/uploads/default/original/3X/e/3/e31b2c251d3ad620b1a6af2bf75f80a628263267.mp3</t>
+        </is>
+      </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/engine-thebangs</t>
@@ -15341,7 +16549,11 @@
           <t>sample + sequencer + splicer in the style of po-33</t>
         </is>
       </c>
-      <c r="E315" s="2" t="inlineStr"/>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/545281946</t>
+        </is>
+      </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/thirtythree/44702</t>
@@ -15387,7 +16599,11 @@
           <t>fractal sequencer for norns + grid</t>
         </is>
       </c>
-      <c r="E316" s="2" t="inlineStr"/>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ef2TC19uK3E?si=RrgsPfO8qXZg2gee</t>
+        </is>
+      </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/thorns-a-fractal-sequencer/73644</t>
@@ -15437,7 +16653,11 @@
           <t>sample player engine and scripts</t>
         </is>
       </c>
-      <c r="E317" s="2" t="inlineStr"/>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Bs4PuShBTbZ</t>
+        </is>
+      </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/21407</t>
@@ -15504,7 +16724,11 @@
           <t>https://norns.community/time-rhythm/</t>
         </is>
       </c>
-      <c r="J318" s="2" t="inlineStr"/>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
@@ -15533,7 +16757,11 @@
           <t>grid based delay sequencer</t>
         </is>
       </c>
-      <c r="E319" s="2" t="inlineStr"/>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/track/628734114</t>
+        </is>
+      </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/timeparty/22837</t>
@@ -15583,7 +16811,11 @@
           <t>library for sequencing midi with text</t>
         </is>
       </c>
-      <c r="E320" s="2" t="inlineStr"/>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/503866942</t>
+        </is>
+      </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tmi/40818</t>
@@ -15629,7 +16861,11 @@
           <t>gated audio sequencer</t>
         </is>
       </c>
-      <c r="E321" s="2" t="inlineStr"/>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B9V3djWhUwn</t>
+        </is>
+      </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/torii/30476</t>
@@ -15675,7 +16911,11 @@
           <t>edit of @markeats loom for quickly decoupling motifs from their harmonic framework</t>
         </is>
       </c>
-      <c r="E322" s="2" t="inlineStr"/>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/ByY7ppPgag_/</t>
+        </is>
+      </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/traffic/21262</t>
@@ -15721,7 +16961,11 @@
           <t>4-voice triangle wave drone synth</t>
         </is>
       </c>
-      <c r="E323" s="2" t="inlineStr"/>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qjHoedoSUXY</t>
+        </is>
+      </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/triangles/52662</t>
@@ -15767,7 +17011,11 @@
           <t>Every night, the kingdom crumbles. And our MIDI pattern, is conjured anew.</t>
         </is>
       </c>
-      <c r="E324" s="2" t="inlineStr"/>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sSMW3ABDiJ4</t>
+        </is>
+      </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/tulpamancer</t>
@@ -15834,7 +17082,11 @@
           <t>https://norns.community/tuner/</t>
         </is>
       </c>
-      <c r="J325" s="2" t="inlineStr"/>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
           <t>2024-01-19</t>
@@ -15863,7 +17115,11 @@
           <t>a collection of uncertain delays using norns softcut</t>
         </is>
       </c>
-      <c r="E326" s="2" t="inlineStr"/>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BwwdlZcls4V/</t>
+        </is>
+      </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tunnels/21973</t>
@@ -15909,7 +17165,11 @@
           <t>a turntable for norns</t>
         </is>
       </c>
-      <c r="E327" s="2" t="inlineStr"/>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kpuc4MYNU9A</t>
+        </is>
+      </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/a-turntable-for-norns-v3-0-1-brings-supercollider-and-crow-to-the-party/67716</t>
@@ -15955,7 +17215,11 @@
           <t>2x4 complex step sequencer w. free running lfo's</t>
         </is>
       </c>
-      <c r="E328" s="2" t="inlineStr"/>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pI81ISvjST4</t>
+        </is>
+      </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/tviburar/</t>
@@ -16001,7 +17265,11 @@
           <t>random granulator for two samples</t>
         </is>
       </c>
-      <c r="E329" s="2" t="inlineStr"/>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RoFk1_z1m18</t>
+        </is>
+      </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/41703</t>
@@ -16047,7 +17315,11 @@
           <t>randomized dual granular playground, inspired by twine</t>
         </is>
       </c>
-      <c r="E330" s="2" t="inlineStr"/>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>https://soundcloud.com/halfpower/squall</t>
+        </is>
+      </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/twins/71052</t>
@@ -16110,7 +17382,11 @@
           <t>https://norns.community/u/</t>
         </is>
       </c>
-      <c r="J331" s="2" t="inlineStr"/>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
           <t>2022-02-05</t>
@@ -16139,7 +17415,11 @@
           <t>ultra-low frequency oscillator powered by the international space station</t>
         </is>
       </c>
-      <c r="E332" s="2" t="inlineStr"/>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oiesvr00nFQ</t>
+        </is>
+      </c>
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="3" t="inlineStr">
         <is>
@@ -16181,7 +17461,11 @@
           <t>your tapes transmitted thru late-night static and broken antenna frequencies</t>
         </is>
       </c>
-      <c r="E333" s="2" t="inlineStr"/>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XMHBb7v7qSg</t>
+        </is>
+      </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/uhf-norns/21154</t>
@@ -16227,7 +17511,11 @@
           <t>collect and recall voltages</t>
         </is>
       </c>
-      <c r="E334" s="2" t="inlineStr"/>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/849959050</t>
+        </is>
+      </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/vcr/63457</t>
@@ -16277,7 +17565,11 @@
           <t>4 track performance-oriented sample sequencer</t>
         </is>
       </c>
-      <c r="E335" s="2" t="inlineStr"/>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/BydFuPwAhma/</t>
+        </is>
+      </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/vials/23109</t>
@@ -16344,7 +17636,11 @@
           <t>https://norns.community/warmreload/</t>
         </is>
       </c>
-      <c r="J336" s="2" t="inlineStr"/>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K336" s="2" t="inlineStr">
         <is>
           <t>2023-08-09</t>
@@ -16373,7 +17669,11 @@
           <t>assemble a song from TAPE</t>
         </is>
       </c>
-      <c r="E337" s="2" t="inlineStr"/>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/623981771</t>
+        </is>
+      </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/waver/49271</t>
@@ -16419,7 +17719,11 @@
           <t>Window comparator for crow</t>
         </is>
       </c>
-      <c r="E338" s="2" t="inlineStr"/>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>https://llllllll.co/uploads/default/original/3X/6/a/6acc86862992482e2ea4c3b28feeae1a635e6663.mp3</t>
+        </is>
+      </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/window-crowparator/71520</t>
@@ -16469,7 +17773,11 @@
           <t>slow oscillators for crow</t>
         </is>
       </c>
-      <c r="E339" s="2" t="inlineStr"/>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/553165797</t>
+        </is>
+      </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/wobblewobble/45215</t>
@@ -16515,7 +17823,11 @@
           <t>dual asyncronous time-wigglers / echo loopers</t>
         </is>
       </c>
-      <c r="E340" s="2" t="inlineStr"/>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UTj8voI0-98</t>
+        </is>
+      </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/wrms/28954</t>
@@ -16565,7 +17877,11 @@
           <t>xD1 is an FM synth</t>
         </is>
       </c>
-      <c r="E341" s="2" t="inlineStr"/>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/763197892</t>
+        </is>
+      </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/xd1-is-an-fm-synth/59150</t>
@@ -16615,7 +17931,11 @@
           <t>a norns cyberdeck tracker</t>
         </is>
       </c>
-      <c r="E342" s="2" t="inlineStr"/>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8ac2qw9gmaw</t>
+        </is>
+      </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
           <t>https://l.llllllll.co/yggdrasil</t>
@@ -16665,7 +17985,11 @@
           <t>game of life based sequencer</t>
         </is>
       </c>
-      <c r="E343" s="2" t="inlineStr"/>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B0t-nJsBTV2/</t>
+        </is>
+      </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/zellen/21107</t>
@@ -16711,7 +18035,11 @@
           <t>a tracker</t>
         </is>
       </c>
-      <c r="E344" s="2" t="inlineStr"/>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6W9oiyR2XD8</t>
+        </is>
+      </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/zxcvbn/59289</t>
@@ -16746,1146 +18074,1428 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId1110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId1117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId1124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId1139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId1366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId1376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId1402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId1421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1422"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1141"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1423"/>
   </tableParts>
 </worksheet>
 </file>
--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -10999,7 +10999,11 @@
           <t>overdub external audio onto four tape loops</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr"/>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CN6zb2kJG3M/</t>
+        </is>
+      </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/nmquadrodubber</t>
@@ -18916,586 +18920,587 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId844"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId845"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId1109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId1111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId1118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId1136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId1143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId1146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId1153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId1170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId1195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId1197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId1198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId1226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId1239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId1244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId1259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId1270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId1279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId1304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId1312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId1314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId1338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId1343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId1366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId1370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId1376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId1384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId1386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId1393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId1402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId1421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId1367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId1377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId1403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId1422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1423"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1423"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1424"/>
   </tableParts>
 </worksheet>
 </file>
--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -4537,7 +4537,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -4537,7 +4537,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -9699,7 +9699,7 @@
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -14695,7 +14695,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -5211,7 +5211,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17389,7 +17389,7 @@
       <c r="J331" s="2" t="inlineStr"/>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/yobink/021920003-modular-animator</t>
+          <t>https://www.instagram.com/p/B6-3E6qlMBa/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1455,7 +1455,11 @@
           <t>https://norns.community/animator/</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2021-07-23</t>
@@ -1640,7 +1644,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://vimeo.com/312196152</t>
+          <t>https://www.youtube.com/watch?v=7HVTXoYaF0I</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1659,7 +1663,11 @@
           <t>https://norns.community/ash/</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>2023-07-24</t>
@@ -1844,7 +1852,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://vimeo.com/327848801</t>
+          <t>https://www.youtube.com/watch?v=ucVF11lo-m8</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1863,7 +1871,11 @@
           <t>https://norns.community/awake/</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
@@ -1894,9 +1906,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BYjTCWS-B7o
-https://www.youtube.com/watch?v=Gvr3T7gLltM
-https://www.youtube.com/watch?v=ucVF11lo-m8</t>
+          <t>https://www.youtube.com/watch?v=BYjTCWS-B7o</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1915,7 +1925,11 @@
           <t>https://norns.community/awake-passersby/</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2021-07-02</t>
@@ -1946,7 +1960,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://w.soundcloud.com/player/?visual=false&amp;url=https%3A%2F%2Fapi.soundcloud.com%2Ftracks%2F695639185&amp;show_artwork=true&amp;maxheight=166</t>
+          <t>https://soundcloud.com/itwasthewires/101419004-modular-norns-crow</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1965,7 +1979,11 @@
           <t>https://norns.community/awake-rings/</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
           <t>2022-03-24</t>
@@ -2716,8 +2734,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=frNbtfMnP20
-https://www.instagram.com/reel/CxoFp1WtMoe/?utm_source=ig_web_copy_link&amp;igshid=MzRlODBiNWFlZA==</t>
+          <t>https://www.youtube.com/watch?v=frNbtfMnP20</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2736,7 +2753,11 @@
           <t>https://norns.community/blue/</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
           <t>2023-09-23</t>
@@ -2929,7 +2950,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JS-_MYMZEOk</t>
+          <t>https://www.instagram.com/p/CIyx5DNHZvK/</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2952,7 +2973,11 @@
           <t>https://norns.community/breakthrough/</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
           <t>2021-01-04</t>
@@ -3083,7 +3108,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=MnD8stNB5tE</t>
+          <t>https://williamhazard.co/sounds/tracks/cdnorns-demo.mp3</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3102,7 +3127,11 @@
           <t>https://norns.community/cartersdelay/</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
           <t>2024-09-12</t>
@@ -3131,11 +3160,7 @@
           <t>fifteen midi cc sliders with slewing and recall</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>https://vimeo.com/913013027</t>
-        </is>
-      </c>
+      <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/66147</t>
@@ -3152,7 +3177,11 @@
           <t>https://norns.community/cc-canvas/</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>2024-02-13</t>
@@ -3233,7 +3262,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1vv2tinYUNo</t>
+          <t>https://www.instagram.com/p/CBwHD-ABSSj/</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -3252,7 +3281,11 @@
           <t>https://norns.community/changes/</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
           <t>2020-08-21</t>
@@ -3283,7 +3316,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>https://vimeo.com/480411843</t>
+          <t>https://www.youtube.com/watch?v=5P0vzHSHA0I</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3306,7 +3339,11 @@
           <t>https://norns.community/cheat_codes_2/</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
@@ -3787,7 +3824,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/675154727</t>
+          <t>https://www.youtube.com/watch?v=Xjv0fVLBLqs</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3810,7 +3847,11 @@
           <t>https://norns.community/compass/</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
           <t>2020-07-29</t>
@@ -3895,7 +3936,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Exploring Norns Ambient Soundscape #3 (Norns Shield) + Microcosm - Constellations - YouTube</t>
+          <t>https://www.youtube.com/watch?v=QDvZAZct2Q8</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3914,7 +3955,11 @@
           <t>https://norns.community/constellations/</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
           <t>2025-07-24</t>
@@ -3945,7 +3990,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4rL78brYvKA</t>
+          <t>https://www.instagram.com/p/CQVIlcOBQRD/</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3968,7 +4013,11 @@
           <t>https://norns.community/corners/</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
           <t>2021-06-23</t>
@@ -4365,7 +4414,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/970754032</t>
+          <t>https://soundcloud.com/cdrake90/delayyyyyyyy-norns-demo</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -4384,7 +4433,11 @@
           <t>https://norns.community/delayyyyyyyy/</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
           <t>2021-01-18</t>
@@ -4413,11 +4466,7 @@
           <t>a sequencer but with a mind of its own</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=neXswJJcatc&amp;t=99s</t>
-        </is>
-      </c>
+      <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/delinquencer-a-sequencer-but-with-a-mind-of-its-own/</t>
@@ -4434,7 +4483,11 @@
           <t>https://norns.community/delinquencer/</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>2024-06-13</t>
@@ -4484,7 +4537,11 @@
           <t>https://norns.community/demoncore/</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>2021-03-30</t>
@@ -4723,7 +4780,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=tGZtcpLYWJY</t>
+          <t>https://soundcloud.com/yncywy/drift</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -4742,7 +4799,11 @@
           <t>https://norns.community/drift/</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
           <t>2020-09-14</t>
@@ -4877,7 +4938,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/668182244</t>
+          <t>https://soundcloud.com/itwasthewires/081919002-norns-dunes</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -4896,7 +4957,11 @@
           <t>https://norns.community/dunes/</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
           <t>2022-05-20</t>
@@ -6267,7 +6332,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QspuCt1FM9M</t>
+          <t>https://vimeo.com/551661371</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -6286,7 +6351,11 @@
           <t>https://norns.community/glaciers/</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
           <t>2023-06-06</t>
@@ -6675,7 +6744,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/809326801</t>
+          <t>https://soundcloud.com/cdrake90/grendy-for-monome-norns-demo</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -6694,7 +6763,11 @@
           <t>https://norns.community/grendy/</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
           <t>2021-02-22</t>
@@ -7241,7 +7314,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ue4eXW6ywDM</t>
+          <t>https://www.youtube.com/watch?v=1DBv-XeEQo8</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -7260,7 +7333,11 @@
           <t>https://norns.community/here-there/</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
           <t>2020-10-01</t>
@@ -7645,7 +7722,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/977550862</t>
+          <t>https://soundcloud.com/user-455170203/initenere-on-monome-norns-with-op-1</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -7668,7 +7745,11 @@
           <t>https://norns.community/initenere/</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
           <t>2022-04-04</t>
@@ -8411,7 +8492,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z61m8jPcQTA</t>
+          <t>https://www.youtube.com/watch?v=kXnI1K2vAh8</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -8430,7 +8511,11 @@
           <t>https://norns.community/lamellae/</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
@@ -9023,7 +9108,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>https://youtu.be/aaKB7Us2Vl8</t>
+          <t>https://www.youtube.com/watch?v=aaKB7Us2Vl8</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -9042,7 +9127,11 @@
           <t>https://norns.community/m18s/</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
           <t>2020-07-26</t>
@@ -9381,7 +9470,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>https://vimeo.com/146731772</t>
+          <t>https://www.youtube.com/watch?v=DjUp1z7a8q8</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -9400,7 +9489,11 @@
           <t>https://norns.community/meadowphysics/</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
           <t>2022-06-04</t>
@@ -9781,7 +9874,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>https://vimeo.com/266741634</t>
+          <t>https://www.youtube.com/watch?v=0sLX6baLqYw</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -9800,7 +9893,11 @@
           <t>https://norns.community/mlr/</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
           <t>2022-07-05</t>
@@ -10189,7 +10286,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>https://w.soundcloud.com/player/?visual=false&amp;url=https%3A%2F%2Fapi.soundcloud.com%2Ftracks%2F983475475&amp;show_artwork=true&amp;maxheight=166</t>
+          <t>https://soundcloud.com/cdrake90/mouse-norns-demo</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -10208,7 +10305,11 @@
           <t>https://norns.community/mouse/</t>
         </is>
       </c>
-      <c r="J190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
           <t>2021-03-04</t>
@@ -10741,11 +10842,7 @@
           <t>norns/circle/02 rhythm and sound</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>https://vimeo.com/416730766</t>
-        </is>
-      </c>
+      <c r="E201" s="3" t="n"/>
       <c r="F201" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-circle-02-rhythm-and-sound/31645</t>
@@ -10762,7 +10859,11 @@
           <t>https://norns.community/nc02-rs/</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
           <t>2020-06-09</t>
@@ -10793,7 +10894,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/sound-and-process/scarlet</t>
+          <t>https://soundcloud.com/tomw/sequin-racer</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -10812,7 +10913,11 @@
           <t>https://norns.community/nc03-ds/</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
           <t>2023-02-06</t>
@@ -11016,7 +11121,11 @@
           <t>https://norns.community/nmMelodyMagic/</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
           <t>2021-07-02</t>
@@ -11357,11 +11466,7 @@
           <t>remotely control norns from the browser</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>https://vimeo.com/484176216</t>
-        </is>
-      </c>
+      <c r="E213" s="3" t="n"/>
       <c r="F213" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-online/38547</t>
@@ -11378,7 +11483,11 @@
           <t>https://norns.community/nornsonline/</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
           <t>2021-12-30</t>
@@ -12217,7 +12326,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g2vcoW4MjbI</t>
+          <t>https://vimeo.com/751029202</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -12236,7 +12345,11 @@
           <t>https://norns.community/overwintering/</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr"/>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
@@ -12375,7 +12488,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EZBpxkxJg0o</t>
+          <t>https://llllllll.co/uploads/default/original/3X/2/1/21240cef99b31da48a50d8ec68ed482dfcb5d6c5.mp3</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -12398,7 +12511,11 @@
           <t>https://norns.community/paranibbles/</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
           <t>2025-09-21</t>
@@ -13759,11 +13876,7 @@
           <t>Randomizer for Dreadbox Typhon</t>
         </is>
       </c>
-      <c r="E260" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=hD-t4onIJbk</t>
-        </is>
-      </c>
+      <c r="E260" s="3" t="n"/>
       <c r="F260" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/randomizer-typhon/54196</t>
@@ -13780,7 +13893,11 @@
           <t>https://norns.community/randomizer_typhon/</t>
         </is>
       </c>
-      <c r="J260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
           <t>2022-04-14</t>
@@ -13959,7 +14076,11 @@
           <t>textural delay orchestra with multiple tempo-synced lines. port of the original by Bryant Smith.</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr"/>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AhKVDUIRt5I</t>
+        </is>
+      </c>
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="3" t="inlineStr">
         <is>
@@ -13976,7 +14097,11 @@
           <t>https://norns.community/repeater/</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr"/>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
           <t>2025-12-18</t>
@@ -14184,7 +14309,11 @@
           <t>https://norns.community/rpmate/</t>
         </is>
       </c>
-      <c r="J268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
           <t>2022-08-09</t>
@@ -14679,7 +14808,11 @@
           <t>compositional interface for music, voltage, and video</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr"/>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sDeOvZlGJTs</t>
+        </is>
+      </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="3" t="inlineStr">
         <is>
@@ -14692,7 +14825,11 @@
           <t>https://norns.community/seeker_ii/</t>
         </is>
       </c>
-      <c r="J278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
           <t>2026-05-24</t>
@@ -15023,7 +15160,7 @@
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/885593155</t>
+          <t>https://soundcloud.com/oehmland/the-blood-rain-comes-and-passes</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -15046,7 +15183,11 @@
           <t>https://norns.community/showers/</t>
         </is>
       </c>
-      <c r="J285" s="2" t="inlineStr"/>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
           <t>2020-11-17</t>
@@ -15285,7 +15426,7 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=G8dZLtmcJ60</t>
+          <t>https://www.youtube.com/watch?v=lia3icu_fCo</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -15304,7 +15445,11 @@
           <t>https://norns.community/smash/</t>
         </is>
       </c>
-      <c r="J290" s="2" t="inlineStr"/>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
           <t>2021-09-19</t>
@@ -15539,7 +15684,7 @@
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Zp7DKJaQs9o</t>
+          <t>https://llllllll.co/uploads/default/original/3X/e/b/ebc0e3da3d1d9db7dedeef7fe8dff0c11862d0af.wav</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -15558,7 +15703,11 @@
           <t>https://norns.community/stack/</t>
         </is>
       </c>
-      <c r="J295" s="2" t="inlineStr"/>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
           <t>2021-02-19</t>
@@ -15843,7 +15992,7 @@
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HgFYZcr8_xY</t>
+          <t>https://www.youtube.com/watch?v=Uwdn_cRO0Mk</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -15866,7 +16015,11 @@
           <t>https://norns.community/stwnsh/</t>
         </is>
       </c>
-      <c r="J301" s="2" t="inlineStr"/>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
           <t>2024-10-23</t>
@@ -16451,7 +16604,7 @@
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/1391254177</t>
+          <t>https://soundcloud.com/user-246275786/tetrabobo-study-01</t>
         </is>
       </c>
       <c r="F313" s="3" t="inlineStr">
@@ -16470,7 +16623,11 @@
           <t>https://norns.community/tetrabobo/</t>
         </is>
       </c>
-      <c r="J313" s="2" t="inlineStr"/>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -16809,7 +16966,7 @@
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>https://soundcloud.com/track/628734114</t>
+          <t>https://soundcloud.com/itwasthewires/052919004-norns-timeparty</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr">
@@ -16832,7 +16989,11 @@
           <t>https://norns.community/timeparty/</t>
         </is>
       </c>
-      <c r="J320" s="2" t="inlineStr"/>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
           <t>2020-05-04</t>
@@ -17013,7 +17174,7 @@
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qjHoedoSUXY</t>
+          <t>https://www.youtube.com/watch?v=aZWNU3KHQ2E</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr">
@@ -17032,7 +17193,11 @@
           <t>https://norns.community/triangles/</t>
         </is>
       </c>
-      <c r="J324" s="2" t="inlineStr"/>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
           <t>2022-03-06</t>
@@ -18333,1223 +18498,1220 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId1105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId1107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId1113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId1127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId1137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId1140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId1142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId1157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId1184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId1194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId1195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId1209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId1230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId1240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId1243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId1256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId1274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId1283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId1308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId1310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId1321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId1339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId1342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId1363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId1367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId1380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId1382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId1388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId1397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId1416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId1422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId1423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId1424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId1425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId1426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId1206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId1360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId1377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId1379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId1413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId1421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId1422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId1423"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1427"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1424"/>
   </tableParts>
 </worksheet>
 </file>
--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -58,14 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1904,7 +1901,7 @@
           <t>time drifting</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=BYjTCWS-B7o</t>
         </is>
@@ -2732,7 +2729,7 @@
           <t>endless waves</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=frNbtfMnP20</t>
         </is>
@@ -3160,7 +3157,11 @@
           <t>fifteen midi cc sliders with slewing and recall</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/913013027</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/66147</t>
@@ -4466,7 +4467,11 @@
           <t>a sequencer but with a mind of its own</t>
         </is>
       </c>
-      <c r="E77" s="3" t="n"/>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=neXswJJcatc&amp;t=99s</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/delinquencer-a-sequencer-but-with-a-mind-of-its-own/</t>
@@ -10842,7 +10847,11 @@
           <t>norns/circle/02 rhythm and sound</t>
         </is>
       </c>
-      <c r="E201" s="3" t="n"/>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/416730766</t>
+        </is>
+      </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-circle-02-rhythm-and-sound/31645</t>
@@ -11466,7 +11475,11 @@
           <t>remotely control norns from the browser</t>
         </is>
       </c>
-      <c r="E213" s="3" t="n"/>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/484176216</t>
+        </is>
+      </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/norns-online/38547</t>
@@ -13876,7 +13889,11 @@
           <t>Randomizer for Dreadbox Typhon</t>
         </is>
       </c>
-      <c r="E260" s="3" t="n"/>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hD-t4onIJbk</t>
+        </is>
+      </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
           <t>https://llllllll.co/t/randomizer-typhon/54196</t>
@@ -14076,7 +14093,7 @@
           <t>textural delay orchestra with multiple tempo-synced lines. port of the original by Bryant Smith.</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E264" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AhKVDUIRt5I</t>
         </is>
@@ -14808,7 +14825,7 @@
           <t>compositional interface for music, voltage, and video</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E278" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sDeOvZlGJTs</t>
         </is>
@@ -18498,1220 +18515,1225 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId1109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId1123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId1133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId1136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId1138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId1141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId1154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId1181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId1191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId1192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId1206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId1227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId1237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId1240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId1253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId1271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId1280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId1305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId1307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId1318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId1336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId1339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId1360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId1364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId1377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId1379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId1385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId1394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId1413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId1419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId1420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId1421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId1422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId1423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId1204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId1205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId1206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId1208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId1210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId1211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId1213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId1214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId1215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId1217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId1219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId1221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId1223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId1350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId1351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId1353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId1354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId1355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId1357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId1358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId1359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId1365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId1366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId1367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId1369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId1373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId1375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId1376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId1377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId1379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId1380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId1390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId1391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId1395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId1396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId1398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId1400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId1402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId1403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId1406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId1407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId1410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId1411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId1412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId1413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId1421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId1422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId1423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId1424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId1425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId1426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId1427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId1428"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1424"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1429"/>
   </tableParts>
 </worksheet>
 </file>
--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -811,7 +811,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>sequencer, midi, generative</t>
+          <t>sequencer, midi, generative, norns only</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>norns, generative, art, drone</t>
+          <t>norns, generative, art, drone, norns only</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>sequencer</t>
+          <t>sequencer, norns only</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>synth</t>
+          <t>synth, norns only</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>sequencer, generative, synth, midi</t>
+          <t>sequencer, generative, synth, midi, norns only</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>synth</t>
+          <t>synth, norns only</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>art, norns only</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>sequencer, generative, midi</t>
+          <t>sequencer, generative, midi, norns only</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>synth, noise</t>
+          <t>synth, noise, norns only</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>synth, drone, generative</t>
+          <t>synth, drone, generative, norns only</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>sequencer, midi</t>
+          <t>sequencer, midi, norns only</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>sequencer, synth</t>
+          <t>sequencer, synth, norns only</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>generative, art, sequencer</t>
+          <t>generative, art, sequencer, norns only</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>synth, midi</t>
+          <t>synth, midi, norns only</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>drum</t>
+          <t>drum, norns only</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>synth, art, midi, noise</t>
+          <t>synth, art, midi, noise, norns only</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>synth, sequencer, midi</t>
+          <t>synth, sequencer, midi, norns only</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>sequencer, midi</t>
+          <t>sequencer, midi, norns only</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>generative, sequencer, midi</t>
+          <t>generative, sequencer, midi, norns only</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>synth, generative, midi</t>
+          <t>synth, generative, midi, norns only</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>sequencer, generative</t>
+          <t>sequencer, generative, norns only</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>art, norns only</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>art, norns only</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>art, norns only</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>synth, midi</t>
+          <t>synth, midi, norns only</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>sequencer, synth</t>
+          <t>sequencer, synth, norns only</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>art, norns only</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>sequencer, generative, synth, art, midi</t>
+          <t>sequencer, generative, synth, art, midi, norns only</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>sequencer, generative, midi</t>
+          <t>sequencer, generative, midi, norns only</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>sequencer, generative, synth, midi</t>
+          <t>sequencer, generative, synth, midi, norns only</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>sequencer, drum</t>
+          <t>sequencer, drum, norns only</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>norns, noise, art, drone</t>
+          <t>norns, noise, art, drone, norns only</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>art, norns only</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>synth, drone, 16n, midi</t>
+          <t>synth, drone, 16n, midi, norns only</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>synth, drone, midi</t>
+          <t>synth, drone, midi, norns only</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>generative, drum</t>
+          <t>generative, drum, norns only</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>synth, sequencer</t>
+          <t>synth, sequencer, norns only</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>drum, synth</t>
+          <t>drum, synth, norns only</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>synth</t>
+          <t>synth, norns only</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -15333,7 +15333,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>synth, drone, 16n, midi, norns only</t>
+          <t>synth, drone, 16n, midi</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -731,7 +731,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -7904,7 +7904,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -1555,7 +1555,11 @@
           <t>https://norns.community/arcify/</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>2019-05-02</t>
@@ -12887,7 +12891,11 @@
           <t>https://norns.community/passthrough/</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>Missing Demo</t>
+        </is>
+      </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
           <t>2022-06-12</t>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17784,7 +17784,7 @@
       <c r="J335" s="2" t="inlineStr"/>
       <c r="K335" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L335" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17784,7 +17784,7 @@
       <c r="J335" s="2" t="inlineStr"/>
       <c r="K335" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L335" s="2" t="inlineStr"/>

--- a/norns_scripts_discourse.xlsx
+++ b/norns_scripts_discourse.xlsx
@@ -17784,7 +17784,7 @@
       <c r="J335" s="2" t="inlineStr"/>
       <c r="K335" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L335" s="2" t="inlineStr"/>
